--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/bio-bio.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4455-876-CM25</t>
+          <t>4020-223-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7753.68</v>
+        <v>3562.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2418-96-CM25</t>
+          <t>3892-113-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3069.31</v>
+        <v>32395.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3604-1123-CM25</t>
+          <t>1305504-49-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.170.501-3</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26655.58</v>
+        <v>27850.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2409-1714-CM25</t>
+          <t>4020-292-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19307.75</v>
+        <v>3679.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2418-94-CM25</t>
+          <t>4074-111-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.150.902-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12730.62</v>
+        <v>9158.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2759-1086-CM25</t>
+          <t>4074-110-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.150.902-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>25320.82</v>
+        <v>11138.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4359-290-CM25</t>
+          <t>4358-82-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8306.18</v>
+        <v>13452.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2762-1244-CM25</t>
+          <t>4494-237-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.151.202-9</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20229.7</v>
+        <v>6643.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2762-1246-CM25</t>
+          <t>4525-247-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.151.202-9</t>
+          <t>69.264.400-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7970.14</v>
+        <v>20080.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4238-317-CM25</t>
+          <t>4239-339-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20657</v>
+        <v>8056.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>654-423-CM25</t>
+          <t>2762-680-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10388.7</v>
+        <v>11803.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2759-1181-CM25</t>
+          <t>2410-380-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2441.88</v>
+        <v>31627.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3604-2249-CM25</t>
+          <t>3892-746-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.170.501-3</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6254.64</v>
+        <v>16362.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3606-207-CM25</t>
+          <t>4081-273-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.967.400-6</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12542.6</v>
+        <v>2374.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4455-1020-CM25</t>
+          <t>1715-95-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9677.809999999999</v>
+        <v>4741.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2409-1891-CM25</t>
+          <t>2418-85-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9661.129999999999</v>
+        <v>5910.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2759-1220-CM25</t>
+          <t>4020-1267-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,28 +1545,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2350.13</v>
+        <v>2870.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3945-1004-CM25</t>
+          <t>4455-840-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1606,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2423.91</v>
+        <v>8381.879999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4055-667-CM25</t>
+          <t>4026-266-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.150.900-1</t>
+          <t>69.250.901-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11392.58</v>
+        <v>3805.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4034-1165-CM25</t>
+          <t>4455-876-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6673.16</v>
+        <v>7753.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2409-2003-CM25</t>
+          <t>2418-96-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7496.88</v>
+        <v>3069.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1242028-61-CM25</t>
+          <t>3604-1123-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.942.400-9</t>
+          <t>69.170.501-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
+          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>559.9</v>
+        <v>26655.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2409-2013-CM25</t>
+          <t>2409-1714-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,43 +1911,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4723.4</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2409-1999-CM25</t>
+          <t>2418-94-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,28 +1972,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7148.6</v>
+        <v>12730.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3737-368-CM25</t>
+          <t>2759-1086-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4924.41</v>
+        <v>25320.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3945-4-CM26</t>
+          <t>4359-290-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,43 +2094,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2166.95</v>
+        <v>8306.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4020-37-CM26</t>
+          <t>2762-1244-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,43 +2155,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>994.96</v>
+        <v>20229.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1305504-7-CM26</t>
+          <t>2762-1246-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,28 +2216,28 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1066.8</v>
+        <v>7970.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2418-2-CM26</t>
+          <t>4238-317-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5704.62</v>
+        <v>20657</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4455-15-CM26</t>
+          <t>654-423-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9330.67</v>
+        <v>10388.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4856-15-CM26</t>
+          <t>2759-1181-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>248.02</v>
+        <v>2441.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4359-7-CM26</t>
+          <t>3604-2249-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.170.501-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,28 +2460,28 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6126.12</v>
+        <v>6254.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4494-34-CM26</t>
+          <t>3606-207-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.967.400-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1039.05</v>
+        <v>12542.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3892-46-CM26</t>
+          <t>4455-1020-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,43 +2582,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3048.88</v>
+        <v>9677.809999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2410-40-CM26</t>
+          <t>2409-1891-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,43 +2643,43 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>11734.66</v>
+        <v>9661.129999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2410-41-CM26</t>
+          <t>2759-1220-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4962.16</v>
+        <v>2350.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2410-43-CM26</t>
+          <t>4055-667-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.150.900-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8032.5</v>
+        <v>11392.58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2408-78-CM26</t>
+          <t>3945-1004-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>25160.98</v>
+        <v>2423.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2408-81-CM26</t>
+          <t>4034-1165-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1872.11</v>
+        <v>6673.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2408-82-CM26</t>
+          <t>1242028-61-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>70.942.400-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35196.06</v>
+        <v>559.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4020-131-CM26</t>
+          <t>2409-2003-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2419.75</v>
+        <v>7496.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1084156-100-CM26</t>
+          <t>2409-2013-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14916.03</v>
+        <v>4723.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2410-53-CM26</t>
+          <t>2409-1999-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>52037.21</v>
+        <v>7148.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1456840-2-CM26</t>
+          <t>3737-368-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>65795.10000000001</v>
+        <v>4924.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3892-70-CM26</t>
+          <t>3945-4-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2598.78</v>
+        <v>2166.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3892-71-CM26</t>
+          <t>4020-37-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3361.63</v>
+        <v>994.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1305504-22-CM26</t>
+          <t>1305504-7-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4145.48</v>
+        <v>1066.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4494-79-CM26</t>
+          <t>2418-2-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6918.66</v>
+        <v>5704.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1084156-116-CM26</t>
+          <t>4455-15-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12198.57</v>
+        <v>9330.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4377-67-CM26</t>
+          <t>4856-15-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.151.100-6</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7777.55</v>
+        <v>248.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1208910-20-CM26</t>
+          <t>4359-7-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28170.51</v>
+        <v>6126.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4020-187-CM26</t>
+          <t>4494-34-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1946.6</v>
+        <v>1039.05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1305504-34-CM26</t>
+          <t>3892-46-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>21442.65</v>
+        <v>3048.88</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4020-200-CM26</t>
+          <t>2410-40-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>799.09</v>
+        <v>11734.66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4377-84-CM26</t>
+          <t>2410-41-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.151.100-6</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>971.28</v>
+        <v>4962.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4377-85-CM26</t>
+          <t>2410-43-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.151.100-6</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>971.28</v>
+        <v>8032.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2418-8-CM26</t>
+          <t>2408-78-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8741.5</v>
+        <v>25160.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4856-66-CM26</t>
+          <t>2408-81-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3256.79</v>
+        <v>1872.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4856-67-CM26</t>
+          <t>2408-82-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>957.36</v>
+        <v>35196.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4020-225-CM26</t>
+          <t>4020-131-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>800.87</v>
+        <v>2419.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4494-128-CM26</t>
+          <t>1084156-100-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4001.97</v>
+        <v>14916.03</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>652-71-CM26</t>
+          <t>2410-53-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5061.07</v>
+        <v>52037.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4351-140-CM26</t>
+          <t>1456840-2-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3378.41</v>
+        <v>65795.10000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>831-71-CM26</t>
+          <t>3892-70-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,27 +4367,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2588.25</v>
+        <v>2598.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4239-104-CM26</t>
+          <t>3892-71-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.160.201-K</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11459.7</v>
+        <v>3361.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3947-273-CM26</t>
+          <t>4494-79-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.151.400-5</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>16193.72</v>
+        <v>6918.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2785-222-CM26</t>
+          <t>1305504-22-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>11888.1</v>
+        <v>4145.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2785-223-CM26</t>
+          <t>1084156-116-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2094.4</v>
+        <v>12198.57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4494-178-CM26</t>
+          <t>4377-67-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.151.100-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7350.63</v>
+        <v>7777.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4455-213-CM26</t>
+          <t>1208910-20-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1784.36</v>
+        <v>28170.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>831-73-CM26</t>
+          <t>4020-187-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8544.200000000001</v>
+        <v>1946.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2418-19-CM26</t>
+          <t>1305504-34-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>17857.85</v>
+        <v>21442.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2410-191-CM26</t>
+          <t>4020-200-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,27 +4916,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8158.76</v>
+        <v>799.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4560-218-CM26</t>
+          <t>4377-84-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,27 +4977,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.160.401-2</t>
+          <t>69.151.100-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>12436.45</v>
+        <v>971.28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4020-320-CM26</t>
+          <t>4377-85-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.151.100-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>792.54</v>
+        <v>971.28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4020-327-CM26</t>
+          <t>2418-8-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1609.71</v>
+        <v>8741.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4239-164-CM26</t>
+          <t>4856-66-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.160.201-K</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>14238.09</v>
+        <v>3256.79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4359-73-CM26</t>
+          <t>4856-67-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>763.98</v>
+        <v>957.36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4020-340-CM26</t>
+          <t>4020-225-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>791</v>
+        <v>800.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4494-217-CM26</t>
+          <t>4494-128-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1536.29</v>
+        <v>4001.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4359-77-CM26</t>
+          <t>652-71-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2684.54</v>
+        <v>5061.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4351-147-CM26</t>
+          <t>4351-140-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>22154.1</v>
+        <v>3378.41</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4079-194-CM26</t>
+          <t>831-71-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ASOPCON LIMITADA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.404.551-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>38017.41</v>
+        <v>2588.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4020-378-CM26</t>
+          <t>4239-104-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2018.84</v>
+        <v>11459.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2421-540-CM26</t>
+          <t>3947-273-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.151.400-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>38384.64</v>
+        <v>16193.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1208910-98-CM26</t>
+          <t>2785-222-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,27 +5709,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1570.28</v>
+        <v>11888.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4020-390-CM26</t>
+          <t>2785-223-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1711.22</v>
+        <v>2094.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4189-246-CM26</t>
+          <t>4494-178-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>13280.19</v>
+        <v>7350.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4055-197-CM26</t>
+          <t>4455-213-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.150.900-1</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>9824.07</v>
+        <v>1784.36</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4493-274-CM26</t>
+          <t>2418-19-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>755.64</v>
+        <v>17857.85</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4081-180-CM26</t>
+          <t>831-73-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,27 +6014,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1530.08</v>
+        <v>8544.200000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4081-181-CM26</t>
+          <t>2410-191-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2295.12</v>
+        <v>8158.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4081-190-CM26</t>
+          <t>4560-218-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,27 +6136,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.160.401-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2024.19</v>
+        <v>12436.45</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4081-191-CM26</t>
+          <t>4020-320-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>674.73</v>
+        <v>792.54</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2759-316-CM26</t>
+          <t>4020-327-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,27 +6258,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3119.44</v>
+        <v>1609.71</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4494-313-CM26</t>
+          <t>4239-164-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7117.72</v>
+        <v>14238.09</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4493-325-CM26</t>
+          <t>4359-73-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>809.2</v>
+        <v>763.98</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2360-358-CM26</t>
+          <t>4494-217-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,27 +6441,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>43311.24</v>
+        <v>1536.29</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4034-269-CM26</t>
+          <t>4020-340-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7767.21</v>
+        <v>791</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4034-276-CM26</t>
+          <t>4359-77-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,27 +6563,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8141.39</v>
+        <v>2684.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3945-373-CM26</t>
+          <t>4351-147-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>41919.88</v>
+        <v>22154.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3085-366-CM26</t>
+          <t>4079-194-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ASOPCON LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.404.551-3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>23944.42</v>
+        <v>38017.41</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2418-38-CM26</t>
+          <t>4020-378-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>17857.85</v>
+        <v>2018.84</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4237-19-CM26</t>
+          <t>2421-540-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>Dirección de Administración de Salud Municipal</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ASOPCON LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.404.551-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>538.48</v>
+        <v>38384.64</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4494-409-CM26</t>
+          <t>1208910-98-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4208.28</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4358-126-CM26</t>
+          <t>4020-390-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,27 +6929,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>65546.72</v>
+        <v>1711.22</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2762-510-CM26</t>
+          <t>4055-197-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.151.202-9</t>
+          <t>69.150.900-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7589.46</v>
+        <v>9824.07</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2421-756-CM26</t>
+          <t>4493-274-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>Ilustre Municipalidad de Penco - Salud</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>11012.63</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4020-548-CM26</t>
+          <t>4189-246-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1009.42</v>
+        <v>13280.19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4455-437-CM26</t>
+          <t>4081-180-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,27 +7173,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>Ilustre Municipalidad de Cabrero</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5414.33</v>
+        <v>1530.08</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4081-232-CM26</t>
+          <t>4081-181-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>534.3099999999999</v>
+        <v>2295.12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4081-230-CM26</t>
+          <t>4081-190-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1250.19</v>
+        <v>2024.19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2408-614-CM26</t>
+          <t>4081-191-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7356,27 +7356,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>Ilustre Municipalidad de Cabrero</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>14998.02</v>
+        <v>674.73</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4020-586-CM26</t>
+          <t>2759-316-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3011.26</v>
+        <v>3119.44</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4238-237-CM26</t>
+          <t>4494-313-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7478,27 +7478,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>9514.93</v>
+        <v>7117.72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2408-616-CM26</t>
+          <t>4493-325-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>Ilustre Municipalidad de Penco - Salud</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2927.4</v>
+        <v>809.2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1467968-21-CM26</t>
+          <t>2360-358-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>65.633.180-1</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2130.08</v>
+        <v>43311.24</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2408-667-CM26</t>
+          <t>4034-269-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7661,27 +7661,27 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3875.08</v>
+        <v>7767.21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2421-862-CM26</t>
+          <t>4034-276-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7722,27 +7722,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5547.7</v>
+        <v>8141.39</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4020-596-CM26</t>
+          <t>3945-373-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1003.75</v>
+        <v>41919.88</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4083-340-CM26</t>
+          <t>3085-366-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3397.21</v>
+        <v>23944.42</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4494-519-CM26</t>
+          <t>2418-38-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,27 +7905,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5955.59</v>
+        <v>17857.85</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2418-51-CM26</t>
+          <t>4237-19-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,27 +7966,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>ASOPCON LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.404.551-3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>916.3</v>
+        <v>538.48</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4358-140-CM26</t>
+          <t>4494-409-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>18368.08</v>
+        <v>4208.28</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2418-50-CM26</t>
+          <t>4358-126-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9612.82</v>
+        <v>65546.72</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1252675-45-CM26</t>
+          <t>2762-510-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial Región  Biobío</t>
+          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,6 +8194,1165 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
+        <v>7589.46</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4020-548-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>69.160.500-0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANETE</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>1009.42</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2421-756-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Dirección de Administración de Salud Municipal</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>11012.63</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4455-437-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.160.100-5</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>5414.33</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4081-230-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Cabrero</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>1250.19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4081-232-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Cabrero</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>534.3099999999999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2408-614-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>14998.02</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4020-586-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>69.160.500-0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANETE</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>3011.26</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4238-237-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>69.160.202-8</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>9514.93</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2408-616-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>2927.4</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1467968-21-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>65.633.180-1</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CORPORACION CULTURAL DE SAN PEDRO DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>2130.08</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2408-667-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>3875.08</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2421-862-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Dirección de Administración de Salud Municipal</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>5547.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4020-596-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>69.160.500-0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANETE</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>1003.75</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4083-340-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>69.151.002-6</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>3397.21</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4494-519-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>69.150.500-6</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCO</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>5955.59</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2418-51-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>COBROTECH SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>916.3</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2418-50-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>9612.82</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4358-140-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>69.170.701-6</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>18368.08</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1252675-45-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial Región  Biobío</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
         <v>15083.61</v>
       </c>
     </row>
